--- a/data/trans_camb/Q45B_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/Q45B_R-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,1</t>
+          <t>0,03; 2,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 2,19</t>
+          <t>0,14; 2,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 0,72</t>
+          <t>-3,46; 0,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 0,63</t>
+          <t>-3,78; 0,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,93</t>
+          <t>-1,43; 1,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,81</t>
+          <t>-1,35; 0,88</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-36,88; —</t>
+          <t>-45,72; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-41,1; —</t>
+          <t>-28,06; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-61,67; 20,04</t>
+          <t>-60,2; 24,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-60,22; 16,7</t>
+          <t>-61,5; 10,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,13; 44,27</t>
+          <t>-43,68; 53,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,24; 39,75</t>
+          <t>-43,33; 42,39</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,03</t>
+          <t>-1,4; 0,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,02</t>
+          <t>-2,14; -0,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 0,99</t>
+          <t>-3,73; 1,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,1; -2,83</t>
+          <t>-7,18; -2,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,68</t>
+          <t>-2,11; 0,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,13; -1,75</t>
+          <t>-4,27; -1,89</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-55,25; 96,16</t>
+          <t>-60,22; 87,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-86,03; 11,6</t>
+          <t>-88,14; 2,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,12; 13,59</t>
+          <t>-37,37; 17,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-71,26; -39,59</t>
+          <t>-71,36; -36,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,58; 15,37</t>
+          <t>-35,55; 19,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,46; -38,41</t>
+          <t>-71,28; -41,19</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 3,66</t>
+          <t>-0,23; 3,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; -0,06</t>
+          <t>-2,91; -0,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,73</t>
+          <t>-1,01; 4,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,1; -0,74</t>
+          <t>-4,92; -0,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 3,04</t>
+          <t>-0,18; 3,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; -0,84</t>
+          <t>-3,27; -0,85</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,54; 319,43</t>
+          <t>-13,16; 307,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-93,13; 17,37</t>
+          <t>-92,95; -2,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,16; 77,83</t>
+          <t>-15,34; 89,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-67,87; -10,74</t>
+          <t>-68,41; -15,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 91,44</t>
+          <t>-4,5; 97,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,58; -26,63</t>
+          <t>-69,33; -26,09</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,8</t>
+          <t>-1,81; 1,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,83; -1,11</t>
+          <t>-3,86; -1,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 2,4</t>
+          <t>-2,9; 2,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,66; -4,14</t>
+          <t>-8,7; -4,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,59</t>
+          <t>-1,7; 1,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,95; -3,26</t>
+          <t>-5,9; -3,15</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,36; 62,79</t>
+          <t>-40,45; 60,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-84,9; -36,59</t>
+          <t>-84,46; -39,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-22,54; 27,27</t>
+          <t>-23,74; 29,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-74,06; -45,87</t>
+          <t>-74,14; -47,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 24,53</t>
+          <t>-22,23; 26,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-74,03; -50,77</t>
+          <t>-73,8; -48,48</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,26</t>
+          <t>-0,26; 1,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,73; -0,51</t>
+          <t>-1,69; -0,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,89</t>
+          <t>-1,76; 0,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,34; -3,15</t>
+          <t>-5,45; -3,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,85</t>
+          <t>-0,77; 0,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,26; -1,96</t>
+          <t>-3,36; -2,01</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 70,85</t>
+          <t>-11,06; 79,75</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-69,95; -27,59</t>
+          <t>-69,2; -27,51</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,45; 12,06</t>
+          <t>-20,42; 13,24</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-63,85; -44,43</t>
+          <t>-63,45; -43,78</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 18,75</t>
+          <t>-14,2; 16,85</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-61,9; -44,32</t>
+          <t>-62,24; -44,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Q45B_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/Q45B_R-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,07</t>
+          <t>0,11; 2,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,08</t>
+          <t>-0,02; 2,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 0,79</t>
+          <t>-3,6; 0,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 0,34</t>
+          <t>-3,54; 0,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,02</t>
+          <t>-1,35; 0,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,88</t>
+          <t>-1,42; 0,92</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-45,72; —</t>
+          <t>-52,42; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-28,06; —</t>
+          <t>-43,36; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-60,2; 24,0</t>
+          <t>-58,21; 15,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-61,5; 10,46</t>
+          <t>-60,2; 15,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,68; 53,23</t>
+          <t>-42,51; 47,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,33; 42,39</t>
+          <t>-46,39; 44,96</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,99</t>
+          <t>-1,35; 1,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; -0,12</t>
+          <t>-2,09; -0,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 1,26</t>
+          <t>-3,66; 1,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,18; -2,67</t>
+          <t>-7,31; -3,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,85</t>
+          <t>-2,28; 0,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,27; -1,89</t>
+          <t>-4,2; -1,74</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-60,22; 87,13</t>
+          <t>-58,2; 103,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-88,14; 2,12</t>
+          <t>-85,12; 8,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-37,37; 17,09</t>
+          <t>-37,66; 16,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-71,36; -36,48</t>
+          <t>-71,69; -39,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,55; 19,37</t>
+          <t>-36,63; 11,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,28; -41,19</t>
+          <t>-70,18; -40,06</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 3,48</t>
+          <t>-0,15; 3,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,91; -0,23</t>
+          <t>-2,71; -0,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 4,23</t>
+          <t>-1,21; 4,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,92; -0,77</t>
+          <t>-5,11; -0,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,15</t>
+          <t>-0,2; 3,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,27; -0,85</t>
+          <t>-3,27; -0,71</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 307,25</t>
+          <t>-14,67; 303,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-92,95; -2,65</t>
+          <t>-93,13; -3,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 89,92</t>
+          <t>-17,25; 88,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-68,41; -15,18</t>
+          <t>-68,61; -12,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 97,31</t>
+          <t>-4,73; 93,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,33; -26,09</t>
+          <t>-71,13; -20,48</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,64</t>
+          <t>-1,72; 1,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,86; -1,18</t>
+          <t>-4,01; -1,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 2,68</t>
+          <t>-2,86; 2,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,7; -4,28</t>
+          <t>-8,88; -4,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 1,7</t>
+          <t>-1,56; 1,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,9; -3,15</t>
+          <t>-5,86; -3,03</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,45; 60,34</t>
+          <t>-39,52; 63,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-84,46; -39,39</t>
+          <t>-85,2; -41,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,74; 29,78</t>
+          <t>-24,1; 25,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-74,14; -47,05</t>
+          <t>-74,61; -46,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 26,83</t>
+          <t>-20,08; 25,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-73,8; -48,48</t>
+          <t>-73,83; -48,38</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,32</t>
+          <t>-0,18; 1,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,69; -0,5</t>
+          <t>-1,67; -0,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,93</t>
+          <t>-1,63; 0,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,45; -3,15</t>
+          <t>-5,3; -3,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,79</t>
+          <t>-0,81; 0,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,36; -2,01</t>
+          <t>-3,36; -2,06</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 79,75</t>
+          <t>-8,07; 74,54</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-69,2; -27,51</t>
+          <t>-69,15; -30,29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,42; 13,24</t>
+          <t>-19,29; 12,49</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-63,45; -43,78</t>
+          <t>-62,81; -45,11</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 16,85</t>
+          <t>-14,77; 16,69</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-62,24; -44,25</t>
+          <t>-62,65; -45,22</t>
         </is>
       </c>
     </row>
